--- a/out/LSTM_Base_repeat_2_000007.xlsx
+++ b/out/LSTM_Base_repeat_2_000007.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.034846904977811</v>
+        <v>8.62785843586423</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.034846904977811</v>
+        <v>8.62785843586423</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>-1.034846904977811</v>
+        <v>9.227858435864231</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA5" t="n">
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-1.034846904977811</v>
+        <v>0.0804624974787484</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.034846904977811</v>
+        <v>0.0804624974787484</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>2.967222099549092</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>2.967222099549092</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>2.967222099549092</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>2.967222099549092</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>2.967222099549092</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>2.967222099549092</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.434846904977811</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>2.367222099549092</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>2.367222099549092</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>2.967222099549092</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>2.967222099549092</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>2.367222099549092</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>2.967222099549092</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>2.967222099549092</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,13 +31946,13 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>2.967222099549092</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC39" t="n">
-        <v>-0.000326274764255737</v>
+        <v>-6.038105188275221e-05</v>
       </c>
     </row>
     <row r="40">
@@ -32733,7 +32733,7 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>3.761466079279133</v>
+        <v>0.6961042754547568</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
@@ -32741,13 +32741,13 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>2.967222099549092</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC40" t="n">
-        <v>7.528746857845212</v>
+        <v>1.393284754049746</v>
       </c>
     </row>
     <row r="41">
@@ -33528,7 +33528,7 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>0.564048617644077</v>
+        <v>0.1043839412694196</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
@@ -33536,13 +33536,13 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>2.967222099549092</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC41" t="n">
-        <v>4.890329502892802</v>
+        <v>0.9050139873536248</v>
       </c>
     </row>
     <row r="42">
@@ -34323,7 +34323,7 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0.7052443583469603</v>
+        <v>0.1305139476654237</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
@@ -34334,10 +34334,10 @@
         <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.434846904977811</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC42" t="n">
-        <v>5.73685913142323</v>
+        <v>1.061674472939382</v>
       </c>
     </row>
     <row r="43">
@@ -35118,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>1.010964443138353</v>
+        <v>0.1870911250288232</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
@@ -35126,13 +35126,13 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>2.367222099549092</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC43" t="n">
-        <v>7.053941659959084</v>
+        <v>1.305416430128927</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>1.081531354478557</v>
+        <v>0.2001504448110093</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>2.367222099549092</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC44" t="n">
-        <v>8.206115998121989</v>
+        <v>1.518640143900103</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>1.1462059807531</v>
+        <v>0.2121183915624241</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>2.967222099549092</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC45" t="n">
-        <v>9.417077748548953</v>
+        <v>1.742743104207468</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.5172607752244275</v>
+        <v>0.09572575083263495</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>2.967222099549092</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC46" t="n">
-        <v>9.304442158364093</v>
+        <v>1.721898468050247</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.249813312232402</v>
+        <v>0.04623051919669491</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38309,10 +38309,10 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC47" t="n">
-        <v>9.286402359007754</v>
+        <v>1.71855998084306</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.119029218758542</v>
+        <v>0.02202746602705347</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC48" t="n">
-        <v>9.274447810542327</v>
+        <v>1.716347619634103</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.03526752723368995</v>
+        <v>0.006523580880987169</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC49" t="n">
-        <v>9.22582685764381</v>
+        <v>1.707346355452162</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.02332815412073143</v>
+        <v>0.004313887701662389</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC50" t="n">
-        <v>9.237197224026399</v>
+        <v>1.709447096823808</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.01193824721542652</v>
+        <v>0.002204963193759101</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC51" t="n">
-        <v>9.237729581399288</v>
+        <v>1.709541551479308</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.006104432512246233</v>
+        <v>0.001125481580367856</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC52" t="n">
-        <v>9.237993094516366</v>
+        <v>1.709586259537464</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.00229138883873318</v>
+        <v>0.0004203693234568383</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC53" t="n">
-        <v>9.236467568482174</v>
+        <v>1.70929965271882</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0012465340675013</v>
+        <v>0.0002268266796096673</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC54" t="n">
-        <v>9.236668036727274</v>
+        <v>1.709332699793215</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0005982000324737712</v>
+        <v>0.000106262193078166</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC55" t="n">
-        <v>9.236616285823123</v>
+        <v>1.709319046125635</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.0003679189895078803</v>
+        <v>6.387685822045283e-05</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC56" t="n">
-        <v>9.236754626261149</v>
+        <v>1.70934067507415</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.0001905801399222358</v>
+        <v>3.10279205119908e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC57" t="n">
-        <v>9.236766666355752</v>
+        <v>1.709338859507548</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>8.991384742459189e-05</v>
+        <v>1.29836763541332e-05</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>2.967222099549092</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC58" t="n">
-        <v>9.236755791467916</v>
+        <v>1.709332746370905</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>5.511987975484745e-05</v>
+        <v>6.512317399864405e-06</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>2.967222099549092</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC59" t="n">
-        <v>9.23677735551912</v>
+        <v>1.709332779412467</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>2.297467066328042e-05</v>
+        <v>-3.375548894532629e-07</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.434846904977811</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC60" t="n">
-        <v>9.236766865298437</v>
+        <v>1.70932675070418</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>7.35242988982542e-06</v>
+        <v>-2.941261685029097e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.434846904977811</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC61" t="n">
-        <v>9.236758576529112</v>
+        <v>1.709321066170152</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>1.675769385467227e-06</v>
+        <v>-3.887371769088796e-06</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC62" t="n">
-        <v>9.2367545687232</v>
+        <v>1.709316314894938</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>-2.093548687745288e-06</v>
+        <v>-4.031182895915095e-06</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC63" t="n">
-        <v>9.236748701280515</v>
+        <v>1.709311025747376</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>-4.053889915940302e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC64" t="n">
-        <v>9.236743631925147</v>
+        <v>1.709311003013075</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>-3.735991635587426e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>2.967222099549092</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC65" t="n">
-        <v>9.236739266951179</v>
+        <v>1.709311321293292</v>
       </c>
     </row>
     <row r="66">
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>2.967222099549092</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC66" t="n">
-        <v>9.236740358197634</v>
+        <v>1.709312412539749</v>
       </c>
     </row>
     <row r="67">
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>2.967222099549092</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC67" t="n">
-        <v>9.236739668590499</v>
+        <v>1.709311722932613</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.434846904977811</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC68" t="n">
-        <v>9.236739698902902</v>
+        <v>1.709311753245014</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.434846904977811</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC69" t="n">
-        <v>9.236739509450391</v>
+        <v>1.709311563792504</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC70" t="n">
-        <v>9.236739562497094</v>
+        <v>1.709311616839207</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC71" t="n">
-        <v>9.236739615543796</v>
+        <v>1.70931166988591</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC72" t="n">
-        <v>9.236739577653294</v>
+        <v>1.709311631995408</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC73" t="n">
-        <v>9.236739448825588</v>
+        <v>1.709311503167702</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC74" t="n">
-        <v>9.236739304841681</v>
+        <v>1.709311359183794</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC75" t="n">
-        <v>9.236739145701572</v>
+        <v>1.709311200043685</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC76" t="n">
-        <v>9.236739198748275</v>
+        <v>1.709311253090388</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC77" t="n">
-        <v>9.236739145701572</v>
+        <v>1.709311200043685</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC78" t="n">
-        <v>9.236739145701572</v>
+        <v>1.709311200043685</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC79" t="n">
-        <v>9.236738963827163</v>
+        <v>1.709311018169276</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC80" t="n">
-        <v>9.236739130545372</v>
+        <v>1.709311184887485</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC81" t="n">
-        <v>9.236739327575982</v>
+        <v>1.709311381918095</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC82" t="n">
-        <v>9.236739168435873</v>
+        <v>1.709311222777987</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC83" t="n">
-        <v>9.236739206326375</v>
+        <v>1.709311260668489</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC84" t="n">
-        <v>9.236739403356987</v>
+        <v>1.709311457699099</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC85" t="n">
-        <v>9.236739380622685</v>
+        <v>1.709311434964798</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC86" t="n">
-        <v>9.236739229060676</v>
+        <v>1.70931128340279</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC87" t="n">
-        <v>9.236739153279673</v>
+        <v>1.709311207621786</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC88" t="n">
-        <v>9.236739251794978</v>
+        <v>1.709311306137091</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC89" t="n">
-        <v>9.236739259373078</v>
+        <v>1.709311313715192</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC90" t="n">
-        <v>9.236739524606591</v>
+        <v>1.709311578948705</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC91" t="n">
-        <v>9.236739229060676</v>
+        <v>1.70931128340279</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC92" t="n">
-        <v>9.23673947155989</v>
+        <v>1.709311525902003</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC93" t="n">
-        <v>9.236739554918993</v>
+        <v>1.709311609261107</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>2.967222099549092</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC94" t="n">
-        <v>9.236739388200784</v>
+        <v>1.709311442542898</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.434846904977811</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC95" t="n">
-        <v>9.236739577653294</v>
+        <v>1.709311631995408</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.434846904977811</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC96" t="n">
-        <v>9.236739229060676</v>
+        <v>1.70931128340279</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC97" t="n">
-        <v>9.236739024451966</v>
+        <v>1.709311078794079</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC98" t="n">
-        <v>9.236739138123472</v>
+        <v>1.709311192465585</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC99" t="n">
-        <v>9.236739153279673</v>
+        <v>1.709311207621786</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC100" t="n">
-        <v>9.236738918358562</v>
+        <v>1.709310972700674</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC101" t="n">
-        <v>9.236738978983363</v>
+        <v>1.709311033325477</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC102" t="n">
-        <v>9.236738850155657</v>
+        <v>1.70931090449777</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>2.967222099549092</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC103" t="n">
-        <v>9.236738986561464</v>
+        <v>1.709311040903577</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.434846904977811</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC104" t="n">
-        <v>9.236739160857772</v>
+        <v>1.709311215199886</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.434846904977811</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC105" t="n">
-        <v>9.236739304841681</v>
+        <v>1.709311359183794</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC106" t="n">
-        <v>9.236739138123472</v>
+        <v>1.709311192465585</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC107" t="n">
-        <v>9.236739130545372</v>
+        <v>1.709311184887485</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC108" t="n">
-        <v>9.236738842577557</v>
+        <v>1.70931089691967</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC109" t="n">
-        <v>9.236738857733757</v>
+        <v>1.709310912075871</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC110" t="n">
-        <v>9.236739085076771</v>
+        <v>1.709311139418882</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC111" t="n">
-        <v>9.236739069920567</v>
+        <v>1.709311124262682</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC112" t="n">
-        <v>9.236739176013975</v>
+        <v>1.709311230356087</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC113" t="n">
-        <v>9.236738903202358</v>
+        <v>1.709310957544473</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC114" t="n">
-        <v>9.236739001717664</v>
+        <v>1.709311056059778</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC115" t="n">
-        <v>9.236739153279673</v>
+        <v>1.709311207621786</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC116" t="n">
-        <v>9.236739168435873</v>
+        <v>1.709311222777987</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC117" t="n">
-        <v>9.236739145701572</v>
+        <v>1.709311200043685</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC118" t="n">
-        <v>9.236739229060676</v>
+        <v>1.70931128340279</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC119" t="n">
-        <v>9.236739327575982</v>
+        <v>1.709311381918095</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC120" t="n">
-        <v>9.236739160857772</v>
+        <v>1.709311215199886</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC121" t="n">
-        <v>9.236739145701572</v>
+        <v>1.709311200043685</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC122" t="n">
-        <v>9.23673911538917</v>
+        <v>1.709311169731284</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC123" t="n">
-        <v>9.23673910023297</v>
+        <v>1.709311154575083</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC124" t="n">
-        <v>9.236739138123472</v>
+        <v>1.709311192465585</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC125" t="n">
-        <v>9.236739153279673</v>
+        <v>1.709311207621786</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC126" t="n">
-        <v>9.236739145701572</v>
+        <v>1.709311200043685</v>
       </c>
     </row>
   </sheetData>

--- a/out/LSTM_Base_repeat_2_000007.xlsx
+++ b/out/LSTM_Base_repeat_2_000007.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5438950205562134</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5438950205562134</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5438950205562134</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5438950205562134</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5438950205562134</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5438950205562134</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5438950205562134</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5438950205562134</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5438950205562134</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5438950205562134</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5438950205562134</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5438950205562134</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5438950205562134</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5438950205562134</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5438950205562134</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5438950205562134</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5438950205562134</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5438950205562134</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-1.034846904977811</v>
+        <v>0.4337207519070788</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>2.967222099549092</v>
+        <v>1.211336524370371</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>1</v>
       </c>
       <c r="JB22" t="n">
-        <v>2.967222099549092</v>
+        <v>1.988952296833663</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>2.967222099549092</v>
+        <v>1.988952296833663</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>1</v>
       </c>
       <c r="JB24" t="n">
-        <v>2.967222099549092</v>
+        <v>1.988952296833663</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>2.967222099549092</v>
+        <v>1.988952296833663</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>1</v>
       </c>
       <c r="JB26" t="n">
-        <v>2.967222099549092</v>
+        <v>1.211336524370371</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.434846904977811</v>
+        <v>0.4337207519070788</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-1.034846904977811</v>
+        <v>0.2337207519070787</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>2.367222099549092</v>
+        <v>1.011336524370371</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>2.367222099549092</v>
+        <v>1.788952296833663</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>2.967222099549092</v>
+        <v>1.988952296833663</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>2.967222099549092</v>
+        <v>1.211336524370371</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-1.034846904977811</v>
+        <v>0.2337207519070787</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5438950205562134</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-1.034846904977811</v>
+        <v>0.2337207519070787</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>2.367222099549092</v>
+        <v>1.011336524370371</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>2.967222099549092</v>
+        <v>1.988952296833663</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>2.967222099549092</v>
+        <v>1.988952296833663</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,10 +31949,10 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>2.967222099549092</v>
+        <v>1.988952296833663</v>
       </c>
       <c r="JC39" t="n">
-        <v>-0.000326274764255737</v>
+        <v>-0.0002516737556036096</v>
       </c>
     </row>
     <row r="40">
@@ -32733,7 +32733,7 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>3.761466079279133</v>
+        <v>2.901426703803963</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
@@ -32744,10 +32744,10 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>2.967222099549092</v>
+        <v>1.988952296833663</v>
       </c>
       <c r="JC40" t="n">
-        <v>7.528746857845212</v>
+        <v>5.807338489675168</v>
       </c>
     </row>
     <row r="41">
@@ -33528,7 +33528,7 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>0.564048617644077</v>
+        <v>0.4350818541585435</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
@@ -33539,10 +33539,10 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>2.967222099549092</v>
+        <v>1.211336524370371</v>
       </c>
       <c r="JC41" t="n">
-        <v>4.890329502892802</v>
+        <v>3.772181425885221</v>
       </c>
     </row>
     <row r="42">
@@ -34323,7 +34323,7 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0.7052443583469603</v>
+        <v>0.5439938841783283</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
@@ -34334,10 +34334,10 @@
         <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.434846904977811</v>
+        <v>1.211336524370371</v>
       </c>
       <c r="JC42" t="n">
-        <v>5.73685913142323</v>
+        <v>4.425156502318888</v>
       </c>
     </row>
     <row r="43">
@@ -35118,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>1.010964443138353</v>
+        <v>0.7798128158070565</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
@@ -35129,10 +35129,10 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>2.367222099549092</v>
+        <v>1.011336524370371</v>
       </c>
       <c r="JC43" t="n">
-        <v>7.053941659959084</v>
+        <v>5.441095136163859</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>1.081531354478557</v>
+        <v>0.834245247758612</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>2.367222099549092</v>
+        <v>1.788952296833663</v>
       </c>
       <c r="JC44" t="n">
-        <v>8.206115998121989</v>
+        <v>6.329830957315837</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>1.1462059807531</v>
+        <v>0.8841318127065874</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>2.967222099549092</v>
+        <v>1.988952296833663</v>
       </c>
       <c r="JC45" t="n">
-        <v>9.417077748548953</v>
+        <v>7.263912462299676</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.5172607752244275</v>
+        <v>0.3989915774434356</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>2.967222099549092</v>
+        <v>1.211336524370371</v>
       </c>
       <c r="JC46" t="n">
-        <v>9.304442158364093</v>
+        <v>7.17703042719177</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.249813312232402</v>
+        <v>0.1926953385426402</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38309,10 +38309,10 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-1.034846904977811</v>
+        <v>0.2337207519070787</v>
       </c>
       <c r="JC47" t="n">
-        <v>9.286402359007754</v>
+        <v>7.163115330147665</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.119029218758542</v>
+        <v>0.0918129790145983</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5438950205562134</v>
       </c>
       <c r="JC48" t="n">
-        <v>9.274447810542327</v>
+        <v>7.15389414954213</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.03526752723368995</v>
+        <v>0.02720390843691141</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5438950205562134</v>
       </c>
       <c r="JC49" t="n">
-        <v>9.22582685764381</v>
+        <v>7.116389962134766</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.02332815412073143</v>
+        <v>0.01799389050546614</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5438950205562134</v>
       </c>
       <c r="JC50" t="n">
-        <v>9.237197224026399</v>
+        <v>7.125160592117419</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.01193824721542652</v>
+        <v>0.009207771764544282</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5438950205562134</v>
       </c>
       <c r="JC51" t="n">
-        <v>9.237729581399288</v>
+        <v>7.125570098385533</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.006104432512246233</v>
+        <v>0.004707185465451411</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5438950205562134</v>
       </c>
       <c r="JC52" t="n">
-        <v>9.237993094516366</v>
+        <v>7.12577222441544</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.00229138883873318</v>
+        <v>0.001766867591125371</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5438950205562134</v>
       </c>
       <c r="JC53" t="n">
-        <v>9.236467568482174</v>
+        <v>7.124594196724256</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0012465340675013</v>
+        <v>0.0009602569933925649</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5438950205562134</v>
       </c>
       <c r="JC54" t="n">
-        <v>9.236668036727274</v>
+        <v>7.124747681571439</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0005982000324737712</v>
+        <v>0.0004599170210766221</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5438950205562134</v>
       </c>
       <c r="JC55" t="n">
-        <v>9.236616285823123</v>
+        <v>7.124706617953466</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.0003679189895078803</v>
+        <v>0.0002832988494084668</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5438950205562134</v>
       </c>
       <c r="JC56" t="n">
-        <v>9.236754626261149</v>
+        <v>7.124812286129602</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.0001905801399222358</v>
+        <v>0.0001452878969928759</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-1.034846904977811</v>
+        <v>0.4337207519070786</v>
       </c>
       <c r="JC57" t="n">
-        <v>9.236766666355752</v>
+        <v>7.124820425565637</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>8.991384742459189e-05</v>
+        <v>6.793379854731798e-05</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>2.967222099549092</v>
+        <v>1.211336524370371</v>
       </c>
       <c r="JC58" t="n">
-        <v>9.236755791467916</v>
+        <v>7.12481088086574</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>5.511987975484745e-05</v>
+        <v>4.232841597722033e-05</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>2.967222099549092</v>
+        <v>1.211336524370371</v>
       </c>
       <c r="JC59" t="n">
-        <v>9.23677735551912</v>
+        <v>7.124826572258828</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>2.297467066328042e-05</v>
+        <v>1.598100299746031e-05</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.434846904977811</v>
+        <v>0.4337207519070786</v>
       </c>
       <c r="JC60" t="n">
-        <v>9.236766865298437</v>
+        <v>7.124817340921809</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>7.35242988982542e-06</v>
+        <v>4.264322417369065e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.434846904977811</v>
+        <v>-0.3438950205562133</v>
       </c>
       <c r="JC61" t="n">
-        <v>9.236758576529112</v>
+        <v>7.124809737939007</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>1.675769385467227e-06</v>
+        <v>5.63141154556023e-07</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5438950205562134</v>
       </c>
       <c r="JC62" t="n">
-        <v>9.2367545687232</v>
+        <v>7.124805564767414</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>-2.093548687745288e-06</v>
+        <v>-3.062365791830193e-06</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5438950205562134</v>
       </c>
       <c r="JC63" t="n">
-        <v>9.236748701280515</v>
+        <v>7.124799842488384</v>
       </c>
     </row>
     <row r="64">
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.034846904977811</v>
+        <v>0.2337207519070786</v>
       </c>
       <c r="JC64" t="n">
-        <v>9.236743631925147</v>
+        <v>7.124794773133015</v>
       </c>
     </row>
     <row r="65">
@@ -52619,10 +52619,10 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>2.967222099549092</v>
+        <v>1.211336524370371</v>
       </c>
       <c r="JC65" t="n">
-        <v>9.236739266951179</v>
+        <v>7.124790408159046</v>
       </c>
     </row>
     <row r="66">
@@ -53414,10 +53414,10 @@
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>2.967222099549092</v>
+        <v>1.988952296833663</v>
       </c>
       <c r="JC66" t="n">
-        <v>9.236740358197634</v>
+        <v>7.124791499405504</v>
       </c>
     </row>
     <row r="67">
@@ -54209,10 +54209,10 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>2.967222099549092</v>
+        <v>1.211336524370371</v>
       </c>
       <c r="JC67" t="n">
-        <v>9.236739668590499</v>
+        <v>7.124790809798367</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.434846904977811</v>
+        <v>0.4337207519070786</v>
       </c>
       <c r="JC68" t="n">
-        <v>9.236739698902902</v>
+        <v>7.124790840110769</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.434846904977811</v>
+        <v>-0.3438950205562133</v>
       </c>
       <c r="JC69" t="n">
-        <v>9.236739509450391</v>
+        <v>7.124790650658259</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5438950205562134</v>
       </c>
       <c r="JC70" t="n">
-        <v>9.236739562497094</v>
+        <v>7.124790703704963</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5438950205562134</v>
       </c>
       <c r="JC71" t="n">
-        <v>9.236739615543796</v>
+        <v>7.124790756751665</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5438950205562134</v>
       </c>
       <c r="JC72" t="n">
-        <v>9.236739577653294</v>
+        <v>7.124790718861163</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5438950205562134</v>
       </c>
       <c r="JC73" t="n">
-        <v>9.236739448825588</v>
+        <v>7.124790590033456</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5438950205562134</v>
       </c>
       <c r="JC74" t="n">
-        <v>9.236739304841681</v>
+        <v>7.124790446049548</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5438950205562134</v>
       </c>
       <c r="JC75" t="n">
-        <v>9.236739145701572</v>
+        <v>7.12479028690944</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5438950205562134</v>
       </c>
       <c r="JC76" t="n">
-        <v>9.236739198748275</v>
+        <v>7.124790339956143</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5438950205562134</v>
       </c>
       <c r="JC77" t="n">
-        <v>9.236739145701572</v>
+        <v>7.12479028690944</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5438950205562134</v>
       </c>
       <c r="JC78" t="n">
-        <v>9.236739145701572</v>
+        <v>7.12479028690944</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5438950205562134</v>
       </c>
       <c r="JC79" t="n">
-        <v>9.236738963827163</v>
+        <v>7.124790105035031</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5438950205562134</v>
       </c>
       <c r="JC80" t="n">
-        <v>9.236739130545372</v>
+        <v>7.124790271753239</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5438950205562134</v>
       </c>
       <c r="JC81" t="n">
-        <v>9.236739327575982</v>
+        <v>7.12479046878385</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5438950205562134</v>
       </c>
       <c r="JC82" t="n">
-        <v>9.236739168435873</v>
+        <v>7.124790309643742</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5438950205562134</v>
       </c>
       <c r="JC83" t="n">
-        <v>9.236739206326375</v>
+        <v>7.124790347534243</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5438950205562134</v>
       </c>
       <c r="JC84" t="n">
-        <v>9.236739403356987</v>
+        <v>7.124790544564854</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5438950205562134</v>
       </c>
       <c r="JC85" t="n">
-        <v>9.236739380622685</v>
+        <v>7.124790521830552</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5438950205562134</v>
       </c>
       <c r="JC86" t="n">
-        <v>9.236739229060676</v>
+        <v>7.124790370268544</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5438950205562134</v>
       </c>
       <c r="JC87" t="n">
-        <v>9.236739153279673</v>
+        <v>7.124790294487541</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5438950205562134</v>
       </c>
       <c r="JC88" t="n">
-        <v>9.236739251794978</v>
+        <v>7.124790393002846</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5438950205562134</v>
       </c>
       <c r="JC89" t="n">
-        <v>9.236739259373078</v>
+        <v>7.124790400580946</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5438950205562134</v>
       </c>
       <c r="JC90" t="n">
-        <v>9.236739524606591</v>
+        <v>7.12479066581446</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5438950205562134</v>
       </c>
       <c r="JC91" t="n">
-        <v>9.236739229060676</v>
+        <v>7.124790370268544</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5438950205562134</v>
       </c>
       <c r="JC92" t="n">
-        <v>9.23673947155989</v>
+        <v>7.124790612767756</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.034846904977811</v>
+        <v>0.4337207519070786</v>
       </c>
       <c r="JC93" t="n">
-        <v>9.236739554918993</v>
+        <v>7.124790696126862</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>1</v>
       </c>
       <c r="JB94" t="n">
-        <v>2.967222099549092</v>
+        <v>0.4337207519070786</v>
       </c>
       <c r="JC94" t="n">
-        <v>9.236739388200784</v>
+        <v>7.124790529408653</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.434846904977811</v>
+        <v>0.4337207519070786</v>
       </c>
       <c r="JC95" t="n">
-        <v>9.236739577653294</v>
+        <v>7.124790718861163</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.434846904977811</v>
+        <v>-0.3438950205562133</v>
       </c>
       <c r="JC96" t="n">
-        <v>9.236739229060676</v>
+        <v>7.124790370268544</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.3438950205562133</v>
       </c>
       <c r="JC97" t="n">
-        <v>9.236739024451966</v>
+        <v>7.124790165659833</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5438950205562134</v>
       </c>
       <c r="JC98" t="n">
-        <v>9.236739138123472</v>
+        <v>7.124790279331339</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5438950205562134</v>
       </c>
       <c r="JC99" t="n">
-        <v>9.236739153279673</v>
+        <v>7.124790294487541</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5438950205562134</v>
       </c>
       <c r="JC100" t="n">
-        <v>9.236738918358562</v>
+        <v>7.124790059566429</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5438950205562134</v>
       </c>
       <c r="JC101" t="n">
-        <v>9.236738978983363</v>
+        <v>7.124790120191231</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.034846904977811</v>
+        <v>0.2337207519070786</v>
       </c>
       <c r="JC102" t="n">
-        <v>9.236738850155657</v>
+        <v>7.124789991363524</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>1</v>
       </c>
       <c r="JB103" t="n">
-        <v>2.967222099549092</v>
+        <v>0.4337207519070786</v>
       </c>
       <c r="JC103" t="n">
-        <v>9.236738986561464</v>
+        <v>7.124790127769332</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.434846904977811</v>
+        <v>0.4337207519070786</v>
       </c>
       <c r="JC104" t="n">
-        <v>9.236739160857772</v>
+        <v>7.124790302065641</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.434846904977811</v>
+        <v>-0.3438950205562133</v>
       </c>
       <c r="JC105" t="n">
-        <v>9.236739304841681</v>
+        <v>7.124790446049548</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.3438950205562133</v>
       </c>
       <c r="JC106" t="n">
-        <v>9.236739138123472</v>
+        <v>7.124790279331339</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5438950205562134</v>
       </c>
       <c r="JC107" t="n">
-        <v>9.236739130545372</v>
+        <v>7.124790271753239</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5438950205562134</v>
       </c>
       <c r="JC108" t="n">
-        <v>9.236738842577557</v>
+        <v>7.124789983785424</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5438950205562134</v>
       </c>
       <c r="JC109" t="n">
-        <v>9.236738857733757</v>
+        <v>7.124789998941625</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5438950205562134</v>
       </c>
       <c r="JC110" t="n">
-        <v>9.236739085076771</v>
+        <v>7.124790226284637</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5438950205562134</v>
       </c>
       <c r="JC111" t="n">
-        <v>9.236739069920567</v>
+        <v>7.124790211128436</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5438950205562134</v>
       </c>
       <c r="JC112" t="n">
-        <v>9.236739176013975</v>
+        <v>7.124790317221842</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5438950205562134</v>
       </c>
       <c r="JC113" t="n">
-        <v>9.236738903202358</v>
+        <v>7.124790044410227</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5438950205562134</v>
       </c>
       <c r="JC114" t="n">
-        <v>9.236739001717664</v>
+        <v>7.124790142925533</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5438950205562134</v>
       </c>
       <c r="JC115" t="n">
-        <v>9.236739153279673</v>
+        <v>7.124790294487541</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5438950205562134</v>
       </c>
       <c r="JC116" t="n">
-        <v>9.236739168435873</v>
+        <v>7.124790309643742</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5438950205562134</v>
       </c>
       <c r="JC117" t="n">
-        <v>9.236739145701572</v>
+        <v>7.12479028690944</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5438950205562134</v>
       </c>
       <c r="JC118" t="n">
-        <v>9.236739229060676</v>
+        <v>7.124790370268544</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5438950205562134</v>
       </c>
       <c r="JC119" t="n">
-        <v>9.236739327575982</v>
+        <v>7.12479046878385</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5438950205562134</v>
       </c>
       <c r="JC120" t="n">
-        <v>9.236739160857772</v>
+        <v>7.124790302065641</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5438950205562134</v>
       </c>
       <c r="JC121" t="n">
-        <v>9.236739145701572</v>
+        <v>7.12479028690944</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5438950205562134</v>
       </c>
       <c r="JC122" t="n">
-        <v>9.23673911538917</v>
+        <v>7.124790256597039</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5438950205562134</v>
       </c>
       <c r="JC123" t="n">
-        <v>9.23673910023297</v>
+        <v>7.124790241440838</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5438950205562134</v>
       </c>
       <c r="JC124" t="n">
-        <v>9.236739138123472</v>
+        <v>7.124790279331339</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5438950205562134</v>
       </c>
       <c r="JC125" t="n">
-        <v>9.236739153279673</v>
+        <v>7.124790294487541</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5438950205562134</v>
       </c>
       <c r="JC126" t="n">
-        <v>9.236739145701572</v>
+        <v>7.12479028690944</v>
       </c>
     </row>
   </sheetData>

--- a/out/LSTM_Base_repeat_2_000007.xlsx
+++ b/out/LSTM_Base_repeat_2_000007.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>-0.01961085572838783</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.5438950205562134</v>
+        <v>-1.28</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>-0.01271171309053898</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.5438950205562134</v>
+        <v>-0.8599999999999997</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>-0.007772911339998245</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.5438950205562134</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>-0.001579828560352325</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.5438950205562134</v>
+        <v>-0.3</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>-0.001506328582763672</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.5438950205562134</v>
+        <v>-0.3</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>-0.00272899866104126</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.5438950205562134</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>-0.003603490069508553</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.5438950205562134</v>
+        <v>0.3</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>-0.003305621445178986</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.5438950205562134</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>-0.002521935850381851</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.5438950205562134</v>
+        <v>-0.3</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>-0.001797640696167946</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.5438950205562134</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>-0.001613590866327286</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.5438950205562134</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>-0.001625671982765198</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.5438950205562134</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0</v>
+        <v>-0.000651095062494278</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.5438950205562134</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0</v>
+        <v>-0.000366775318980217</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.5438950205562134</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0</v>
+        <v>-0.0001715440303087234</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.5438950205562134</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0</v>
+        <v>-0.00109594315290451</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.5438950205562134</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>-0.001217197626829147</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.5438950205562134</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>-0.001381434500217438</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.5438950205562134</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0</v>
+        <v>-0.000849233940243721</v>
       </c>
       <c r="JB20" t="n">
-        <v>0.4337207519070788</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>2.087652683258057e-05</v>
       </c>
       <c r="JB21" t="n">
-        <v>1.211336524370371</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0.001852260902523994</v>
       </c>
       <c r="JB22" t="n">
-        <v>1.988952296833663</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0.004976062104105949</v>
       </c>
       <c r="JB23" t="n">
-        <v>1.988952296833663</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0.004083883017301559</v>
       </c>
       <c r="JB24" t="n">
-        <v>1.988952296833663</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0.002008728682994843</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.988952296833663</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0.0004466976970434189</v>
       </c>
       <c r="JB26" t="n">
-        <v>1.211336524370371</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0</v>
+        <v>-0.0003763735294342041</v>
       </c>
       <c r="JB27" t="n">
-        <v>0.4337207519070788</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0</v>
+        <v>-0.0009896960109472275</v>
       </c>
       <c r="JB28" t="n">
-        <v>0.2337207519070787</v>
+        <v>-0.16</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0.0006744712591171265</v>
       </c>
       <c r="JB29" t="n">
-        <v>1.011336524370371</v>
+        <v>-0.16</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0.001689989119768143</v>
       </c>
       <c r="JB30" t="n">
-        <v>1.788952296833663</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0.001132717356085777</v>
       </c>
       <c r="JB31" t="n">
-        <v>1.988952296833663</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0.0005168803036212921</v>
       </c>
       <c r="JB32" t="n">
-        <v>1.211336524370371</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>-0.0003216005861759186</v>
       </c>
       <c r="JB33" t="n">
-        <v>0.2337207519070787</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>-0.0004369132220745087</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.5438950205562134</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0</v>
+        <v>-2.298690378665924e-05</v>
       </c>
       <c r="JB35" t="n">
-        <v>0.2337207519070787</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0.002944260835647583</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.011336524370371</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0.01196565851569176</v>
       </c>
       <c r="JB37" t="n">
-        <v>1.988952296833663</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0.0101102739572525</v>
       </c>
       <c r="JB38" t="n">
-        <v>1.988952296833663</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,13 +31946,13 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0.006713595241308212</v>
       </c>
       <c r="JB39" t="n">
-        <v>1.988952296833663</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC39" t="n">
-        <v>-0.0002516737556036096</v>
+        <v>-0.0001549058461502427</v>
       </c>
     </row>
     <row r="40">
@@ -32733,7 +32733,7 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>2.901426703803963</v>
+        <v>1.78583554918772</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
@@ -32741,13 +32741,13 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0.003312673419713974</v>
       </c>
       <c r="JB40" t="n">
-        <v>1.988952296833663</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC40" t="n">
-        <v>5.807338489675168</v>
+        <v>3.574431829402426</v>
       </c>
     </row>
     <row r="41">
@@ -33528,7 +33528,7 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>0.4350818541585435</v>
+        <v>0.2677940295027282</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
@@ -33536,13 +33536,13 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0.0006476789712905884</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.211336524370371</v>
+        <v>-0.3</v>
       </c>
       <c r="JC41" t="n">
-        <v>3.772181425885221</v>
+        <v>2.321787350753424</v>
       </c>
     </row>
     <row r="42">
@@ -34323,7 +34323,7 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0.5439938841783283</v>
+        <v>0.3348296714205644</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
@@ -34331,13 +34331,13 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0</v>
+        <v>-0.001383058726787567</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.211336524370371</v>
+        <v>-0.3</v>
       </c>
       <c r="JC42" t="n">
-        <v>4.425156502318888</v>
+        <v>2.723695191651274</v>
       </c>
     </row>
     <row r="43">
@@ -35118,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>0.7798128158070565</v>
+        <v>0.4799765834096693</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
@@ -35126,13 +35126,13 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.002760959789156914</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.011336524370371</v>
+        <v>-0.3</v>
       </c>
       <c r="JC43" t="n">
-        <v>5.441095136163859</v>
+        <v>3.349007971857544</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.834245247758612</v>
+        <v>0.5134802186497581</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.007753010839223862</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.788952296833663</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC44" t="n">
-        <v>6.329830957315837</v>
+        <v>3.896027286613095</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.8841318127065874</v>
+        <v>0.5441855350372284</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.01154050230979919</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.988952296833663</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC45" t="n">
-        <v>7.263912462299676</v>
+        <v>4.470956993080633</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.3989915774434356</v>
+        <v>0.2455808107781548</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0.01204202324151993</v>
       </c>
       <c r="JB46" t="n">
-        <v>1.211336524370371</v>
+        <v>-0.16</v>
       </c>
       <c r="JC46" t="n">
-        <v>7.17703042719177</v>
+        <v>4.417480863582146</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.1926953385426402</v>
+        <v>0.1186043069563733</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0</v>
+        <v>-0.001590652391314507</v>
       </c>
       <c r="JB47" t="n">
-        <v>0.2337207519070787</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC47" t="n">
-        <v>7.163115330147665</v>
+        <v>4.40891609780406</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.0918129790145983</v>
+        <v>0.05651142118971724</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>-0.006380587816238403</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.5438950205562134</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC48" t="n">
-        <v>7.15389414954213</v>
+        <v>4.403240444964288</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.02720390843691141</v>
+        <v>0.01674393990492229</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>-0.01302358880639076</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.5438950205562134</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC49" t="n">
-        <v>7.116389962134766</v>
+        <v>4.380156708243582</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.01799389050546614</v>
+        <v>0.01107338432264835</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>-0.01230665668845177</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.5438950205562134</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC50" t="n">
-        <v>7.125160592117419</v>
+        <v>4.385553383028531</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.009207771764544282</v>
+        <v>0.005665533341778137</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>-0.01277822628617287</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.5438950205562134</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC51" t="n">
-        <v>7.125570098385533</v>
+        <v>4.38580351489045</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.004707185465451411</v>
+        <v>0.002895193618022969</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>-0.01015949994325638</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.5438950205562134</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC52" t="n">
-        <v>7.12577222441544</v>
+        <v>4.38592600282335</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.001766867591125371</v>
+        <v>0.001085671165660683</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0</v>
+        <v>-0.00824911892414093</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.5438950205562134</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC53" t="n">
-        <v>7.124594196724256</v>
+        <v>4.385198946905795</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0009602569933925649</v>
+        <v>0.0005890043036261937</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>-0.007185608148574829</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.5438950205562134</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC54" t="n">
-        <v>7.124747681571439</v>
+        <v>4.385291502274408</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0004599170210766221</v>
+        <v>0.0002811027822009983</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>-0.005751077085733414</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.5438950205562134</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC55" t="n">
-        <v>7.124706617953466</v>
+        <v>4.385264297620117</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.0002832988494084668</v>
+        <v>0.0001721119211383073</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>-0.003471359610557556</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.5438950205562134</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC56" t="n">
-        <v>7.124812286129602</v>
+        <v>4.38532747434807</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.0001452878969928759</v>
+        <v>8.764322417369065e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>-0.005059061571955681</v>
       </c>
       <c r="JB57" t="n">
-        <v>0.4337207519070786</v>
+        <v>0.16</v>
       </c>
       <c r="JC57" t="n">
-        <v>7.124820425565637</v>
+        <v>4.385330591440431</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>6.793379854731798e-05</v>
+        <v>3.9959190885333e-05</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0.007339745759963989</v>
       </c>
       <c r="JB58" t="n">
-        <v>1.211336524370371</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC58" t="n">
-        <v>7.12481088086574</v>
+        <v>4.385322778286423</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>4.232841597722033e-05</v>
+        <v>2.442036668854237e-05</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0.004953784868121147</v>
       </c>
       <c r="JB59" t="n">
-        <v>1.211336524370371</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC59" t="n">
-        <v>7.124826572258828</v>
+        <v>4.385330640503748</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>1.598100299746031e-05</v>
+        <v>7.821724054003525e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>-0.00480005145072937</v>
       </c>
       <c r="JB60" t="n">
-        <v>0.4337207519070786</v>
+        <v>0.16</v>
       </c>
       <c r="JC60" t="n">
-        <v>7.124817340921809</v>
+        <v>4.385323010481095</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>4.264322417369065e-06</v>
+        <v>1.176214944912711e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>-0.009200606495141983</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.3438950205562133</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC61" t="n">
-        <v>7.124809737939007</v>
+        <v>4.385316366096433</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>5.63141154556023e-07</v>
+        <v>-1.662115307266386e-06</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>-0.009521383792161942</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.5438950205562134</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC62" t="n">
-        <v>7.124805564767414</v>
+        <v>4.385311862193476</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>-3.062365791830193e-06</v>
+        <v>-4.031182895915095e-06</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>-0.008818097412586212</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.5438950205562134</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC63" t="n">
-        <v>7.124799842488384</v>
+        <v>4.385306429062008</v>
       </c>
     </row>
     <row r="64">
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>-0.004413554444909096</v>
       </c>
       <c r="JB64" t="n">
-        <v>0.2337207519070786</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC64" t="n">
-        <v>7.124794773133015</v>
+        <v>4.38530138244094</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>-3.735991635587426e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0.006406176835298538</v>
       </c>
       <c r="JB65" t="n">
-        <v>1.211336524370371</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC65" t="n">
-        <v>7.124790408159046</v>
+        <v>4.385301700721157</v>
       </c>
     </row>
     <row r="66">
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0.01895894110202789</v>
       </c>
       <c r="JB66" t="n">
-        <v>1.988952296833663</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC66" t="n">
-        <v>7.124791499405504</v>
+        <v>4.385302791967614</v>
       </c>
     </row>
     <row r="67">
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0.007317539304494858</v>
       </c>
       <c r="JB67" t="n">
-        <v>1.211336524370371</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC67" t="n">
-        <v>7.124790809798367</v>
+        <v>4.385302102360478</v>
       </c>
     </row>
     <row r="68">
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>-0.009229779243469238</v>
       </c>
       <c r="JB68" t="n">
-        <v>0.4337207519070786</v>
+        <v>0.16</v>
       </c>
       <c r="JC68" t="n">
-        <v>7.124790840110769</v>
+        <v>4.38530213267288</v>
       </c>
     </row>
     <row r="69">
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>-0.01786051318049431</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.3438950205562133</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC69" t="n">
-        <v>7.124790650658259</v>
+        <v>4.385301943220369</v>
       </c>
     </row>
     <row r="70">
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>-0.01924999617040157</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.5438950205562134</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC70" t="n">
-        <v>7.124790703704963</v>
+        <v>4.385301996267073</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>-0.01924192905426025</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.5438950205562134</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC71" t="n">
-        <v>7.124790756751665</v>
+        <v>4.385302049313776</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>-0.0171041302382946</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.5438950205562134</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC72" t="n">
-        <v>7.124790718861163</v>
+        <v>4.385302011423273</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>-0.01373940519988537</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.5438950205562134</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC73" t="n">
-        <v>7.124790590033456</v>
+        <v>4.385301882595567</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>-0.01137774810194969</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.5438950205562134</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC74" t="n">
-        <v>7.124790446049548</v>
+        <v>4.385301738611659</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>-0.009707644581794739</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.5438950205562134</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC75" t="n">
-        <v>7.12479028690944</v>
+        <v>4.385301579471551</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>-0.00791625864803791</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.5438950205562134</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC76" t="n">
-        <v>7.124790339956143</v>
+        <v>4.385301632518253</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>-0.008064357563853264</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.5438950205562134</v>
+        <v>0.16</v>
       </c>
       <c r="JC77" t="n">
-        <v>7.12479028690944</v>
+        <v>4.385301579471551</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>-0.006687631830573082</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.5438950205562134</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC78" t="n">
-        <v>7.12479028690944</v>
+        <v>4.385301579471551</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>-0.003865359351038933</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.5438950205562134</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC79" t="n">
-        <v>7.124790105035031</v>
+        <v>4.385301397597142</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>-0.001103997230529785</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.5438950205562134</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC80" t="n">
-        <v>7.124790271753239</v>
+        <v>4.38530156431535</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>-0.002827372401952744</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.5438950205562134</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC81" t="n">
-        <v>7.12479046878385</v>
+        <v>4.385301761345961</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>-0.005196364596486092</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.5438950205562134</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC82" t="n">
-        <v>7.124790309643742</v>
+        <v>4.385301602205852</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>-0.002950858324766159</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.5438950205562134</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC83" t="n">
-        <v>7.124790347534243</v>
+        <v>4.385301640096353</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>-0.0005117394030094147</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.5438950205562134</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC84" t="n">
-        <v>7.124790544564854</v>
+        <v>4.385301837126963</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>-0.002918645739555359</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.5438950205562134</v>
+        <v>-0.3</v>
       </c>
       <c r="JC85" t="n">
-        <v>7.124790521830552</v>
+        <v>4.385301814392663</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>-0.005937285721302032</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.5438950205562134</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC86" t="n">
-        <v>7.124790370268544</v>
+        <v>4.385301662830654</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>-0.006349777802824974</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.5438950205562134</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC87" t="n">
-        <v>7.124790294487541</v>
+        <v>4.385301587049651</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0</v>
+        <v>-0.005162013694643974</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.5438950205562134</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC88" t="n">
-        <v>7.124790393002846</v>
+        <v>4.385301685564957</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>-0.001849973574280739</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.5438950205562134</v>
+        <v>-0.16</v>
       </c>
       <c r="JC89" t="n">
-        <v>7.124790400580946</v>
+        <v>4.385301693143057</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>-0.001952383667230606</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.5438950205562134</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC90" t="n">
-        <v>7.12479066581446</v>
+        <v>4.38530195837657</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>-0.00377313420176506</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.5438950205562134</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC91" t="n">
-        <v>7.124790370268544</v>
+        <v>4.385301662830654</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>-0.002042332664132118</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.5438950205562134</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC92" t="n">
-        <v>7.124790612767756</v>
+        <v>4.385301905329867</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>-0.00411687046289444</v>
       </c>
       <c r="JB93" t="n">
-        <v>0.4337207519070786</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC93" t="n">
-        <v>7.124790696126862</v>
+        <v>4.385301988688972</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0.0007407646626234055</v>
       </c>
       <c r="JB94" t="n">
-        <v>0.4337207519070786</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC94" t="n">
-        <v>7.124790529408653</v>
+        <v>4.385301821970764</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>-0.002595392987132072</v>
       </c>
       <c r="JB95" t="n">
-        <v>0.4337207519070786</v>
+        <v>0.3</v>
       </c>
       <c r="JC95" t="n">
-        <v>7.124790718861163</v>
+        <v>4.385302011423273</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>-0.007903372868895531</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.3438950205562133</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC96" t="n">
-        <v>7.124790370268544</v>
+        <v>4.385301662830654</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>-0.01146919839084148</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.3438950205562133</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC97" t="n">
-        <v>7.124790165659833</v>
+        <v>4.385301458221944</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>-0.0110282264649868</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.5438950205562134</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC98" t="n">
-        <v>7.124790279331339</v>
+        <v>4.38530157189345</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>-0.008543390780687332</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.5438950205562134</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC99" t="n">
-        <v>7.124790294487541</v>
+        <v>4.385301587049651</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>-0.007001444697380066</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.5438950205562134</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC100" t="n">
-        <v>7.124790059566429</v>
+        <v>4.385301352128539</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>-0.006861967965960503</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.5438950205562134</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC101" t="n">
-        <v>7.124790120191231</v>
+        <v>4.385301412753342</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>-0.006190121173858643</v>
       </c>
       <c r="JB102" t="n">
-        <v>0.2337207519070786</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC102" t="n">
-        <v>7.124789991363524</v>
+        <v>4.385301283925635</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>8.178874850273132e-05</v>
       </c>
       <c r="JB103" t="n">
-        <v>0.4337207519070786</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC103" t="n">
-        <v>7.124790127769332</v>
+        <v>4.385301420331443</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>-0.0002209413796663284</v>
       </c>
       <c r="JB104" t="n">
-        <v>0.4337207519070786</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC104" t="n">
-        <v>7.124790302065641</v>
+        <v>4.385301594627751</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>-0.002220761030912399</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.3438950205562133</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC105" t="n">
-        <v>7.124790446049548</v>
+        <v>4.385301738611659</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>-0.00275127962231636</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.3438950205562133</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC106" t="n">
-        <v>7.124790279331339</v>
+        <v>4.38530157189345</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>-0.00424191914498806</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.5438950205562134</v>
+        <v>0.3</v>
       </c>
       <c r="JC107" t="n">
-        <v>7.124790271753239</v>
+        <v>4.38530156431535</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>-0.00655512697994709</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.5438950205562134</v>
+        <v>0.16</v>
       </c>
       <c r="JC108" t="n">
-        <v>7.124789983785424</v>
+        <v>4.385301276347534</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>-0.005644191056489944</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.5438950205562134</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC109" t="n">
-        <v>7.124789998941625</v>
+        <v>4.385301291503736</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>-0.004081502556800842</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.5438950205562134</v>
+        <v>-0.3</v>
       </c>
       <c r="JC110" t="n">
-        <v>7.124790226284637</v>
+        <v>4.385301518846748</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>-0.001373343169689178</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.5438950205562134</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC111" t="n">
-        <v>7.124790211128436</v>
+        <v>4.385301503690546</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>-0.002617597579956055</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.5438950205562134</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC112" t="n">
-        <v>7.124790317221842</v>
+        <v>4.385301609783952</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>-0.003877600654959679</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.5438950205562134</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC113" t="n">
-        <v>7.124790044410227</v>
+        <v>4.385301336972338</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0</v>
+        <v>-0.002809926867485046</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.5438950205562134</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC114" t="n">
-        <v>7.124790142925533</v>
+        <v>4.385301435487643</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>-0.001760112121701241</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.5438950205562134</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC115" t="n">
-        <v>7.124790294487541</v>
+        <v>4.385301587049651</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>-0.001568576321005821</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.5438950205562134</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC116" t="n">
-        <v>7.124790309643742</v>
+        <v>4.385301602205852</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>-0.001263033598661423</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.5438950205562134</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC117" t="n">
-        <v>7.12479028690944</v>
+        <v>4.385301579471551</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>-0.000572962686419487</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.5438950205562134</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC118" t="n">
-        <v>7.124790370268544</v>
+        <v>4.385301662830654</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0</v>
+        <v>-0.002129498869180679</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.5438950205562134</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC119" t="n">
-        <v>7.12479046878385</v>
+        <v>4.385301761345961</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>-0.003768416121602058</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.5438950205562134</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC120" t="n">
-        <v>7.124790302065641</v>
+        <v>4.385301594627751</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>-0.004027286544442177</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.5438950205562134</v>
+        <v>-0.16</v>
       </c>
       <c r="JC121" t="n">
-        <v>7.12479028690944</v>
+        <v>4.385301579471551</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>-0.003722669556736946</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.5438950205562134</v>
+        <v>-0.3</v>
       </c>
       <c r="JC122" t="n">
-        <v>7.124790256597039</v>
+        <v>4.385301549159148</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>-0.003223903477191925</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.5438950205562134</v>
+        <v>-0.16</v>
       </c>
       <c r="JC123" t="n">
-        <v>7.124790241440838</v>
+        <v>4.385301534002949</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>-0.003324653953313828</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.5438950205562134</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC124" t="n">
-        <v>7.124790279331339</v>
+        <v>4.38530157189345</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>-0.002535270527005196</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.5438950205562134</v>
+        <v>0.1900000000000003</v>
       </c>
       <c r="JC125" t="n">
-        <v>7.124790294487541</v>
+        <v>4.385301587049651</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>-0.001457901671528816</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.5438950205562134</v>
+        <v>1</v>
       </c>
       <c r="JC126" t="n">
-        <v>7.12479028690944</v>
+        <v>4.385301579471551</v>
       </c>
     </row>
   </sheetData>

--- a/out/LSTM_Base_repeat_2_000007.xlsx
+++ b/out/LSTM_Base_repeat_2_000007.xlsx
@@ -61364,7 +61364,7 @@
         <v>-0.00791625864803791</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.7199999999999999</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC76" t="n">
         <v>4.385301632518253</v>
@@ -62159,7 +62159,7 @@
         <v>-0.008064357563853264</v>
       </c>
       <c r="JB77" t="n">
-        <v>0.16</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC77" t="n">
         <v>4.385301579471551</v>
@@ -62954,7 +62954,7 @@
         <v>-0.006687631830573082</v>
       </c>
       <c r="JB78" t="n">
-        <v>0.4399999999999999</v>
+        <v>0.3</v>
       </c>
       <c r="JC78" t="n">
         <v>4.385301579471551</v>
@@ -63749,7 +63749,7 @@
         <v>-0.003865359351038933</v>
       </c>
       <c r="JB79" t="n">
-        <v>0.7199999999999999</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC79" t="n">
         <v>4.385301397597142</v>
@@ -64544,7 +64544,7 @@
         <v>-0.001103997230529785</v>
       </c>
       <c r="JB80" t="n">
-        <v>0.9999999999999998</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC80" t="n">
         <v>4.38530156431535</v>
@@ -68519,7 +68519,7 @@
         <v>-0.002918645739555359</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.3</v>
+        <v>0.3</v>
       </c>
       <c r="JC85" t="n">
         <v>4.385301814392663</v>
